--- a/yandex-direct/audit/2026-09-28-dnevnik-plan-vse-gruppy.xlsx
+++ b/yandex-direct/audit/2026-09-28-dnevnik-plan-vse-gruppy.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3487" uniqueCount="763">
   <si>
     <t>РК</t>
   </si>
@@ -1107,10 +1107,10 @@
   </si>
   <si>
     <t xml:space="preserve">5 867₽ / 45 кл / 1 лид / CPL 5 867 / отказ 25% / об.трафика 89 / премиум 49% / поз. 2,4
-Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле. У группы есть лид - остановка как дубль, спрос забирает НЧ.</t>
-  </si>
-  <si>
-    <t>14.10 и 04.11: лиды «гармошка» в НЧ не ниже, чем было суммарно в НЧ+СЧ за те же недели</t>
+Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше. У группы есть лид - остановка как дубль, спрос забирает НЧ 5774336420.</t>
+  </si>
+  <si>
+    <t>14.10 и 04.11: лиды по «гармошка» в НЧ не ниже, чем было суммарно в НЧ+СЧ</t>
   </si>
   <si>
     <t>5774336316</t>
@@ -1138,7 +1138,7 @@
   </si>
   <si>
     <t xml:space="preserve">3 936₽ / 37 кл / 1 лид / CPL 3 936 / отказ 29% / об.трафика 87 / премиум 68% / поз. 2,7
-Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле. У группы есть лид - остановка как дубль, спрос забирает НЧ.</t>
+Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше. У группы есть лид - остановка как дубль, спрос забирает НЧ 5774336420.</t>
   </si>
   <si>
     <t>5774336314</t>
@@ -1149,7 +1149,7 @@
   </si>
   <si>
     <t xml:space="preserve">3 892₽ / 43 кл / 1 лид / CPL 3 892 / отказ 28% / об.трафика 88 / премиум 44% / поз. 2,2
-Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле. У группы есть лид - остановка как дубль, спрос забирает НЧ.</t>
+Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше. У группы есть лид - остановка как дубль, спрос забирает НЧ 5774336420.</t>
   </si>
   <si>
     <t>5774336318</t>
@@ -1160,7 +1160,7 @@
   </si>
   <si>
     <t xml:space="preserve">2 042₽ / 15 кл / 0 лид / отказ 10% / об.трафика 85 / премиум 55% / поз. 2,3
-Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле.</t>
+Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше.</t>
   </si>
   <si>
     <t>5774336319</t>
@@ -1171,7 +1171,7 @@
   </si>
   <si>
     <t xml:space="preserve">1 501₽ / 19 кл / 0 лид / отказ 25% / об.трафика 87 / премиум 48% / поз. 2,2
-Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле.</t>
+Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше.</t>
   </si>
   <si>
     <t>5774336317</t>
@@ -1182,7 +1182,7 @@
   </si>
   <si>
     <t xml:space="preserve">1 406₽ / 21 кл / 0 лид / отказ 40% / об.трафика 89 / премиум 55% / поз. 2,2
-Семейство СЧ: 18 644 ₽, 3 лида (по меткам), CPL 6 215 ₽ против 2 417 ₽ у НЧ «Складные». Половина кликов дублирует те же запросы в НЧ. Спрос уходит в НЧ, где он дешевле.</t>
+Один и тот же спрос «гармошка» покупают две РК: запросы с «гармошка» в НЧ - 129 визитов, 5 лидов; в СЧ - 142 визита, 2 лида. В СЧ-гармошках слово «складные» есть лишь в 2 кликах из 179 - это не складные, а именно гармошки и двери-гармошки. Оставляем спрос в НЧ, где он конвертит лучше.</t>
   </si>
   <si>
     <t>5774336315</t>
@@ -1591,14 +1591,14 @@
 Группа № 5774336420 - Складные перегородки | Гармошка</t>
   </si>
   <si>
-    <t>Добавить фразы: «перегородка гармошка», «дверь гармошка», «двери гармошка на заказ», «межкомнатные перегородки гармошка»</t>
+    <t>Добавить фразы (все со словом «гармошка», разделение со «Складными» сохраняется): [перегородка] [гармошка] / [перегородки] [гармошка] [межкомнатные] / [дверь] [гармошка] / [дверь] [гармошка] [заказ]</t>
   </si>
   <si>
     <t xml:space="preserve">16 439₽ / 122 кл / 4 лид / CPL 4 110 / отказ 29% / об.трафика 87 / премиум 76% / поз. 2,6
-Принимающий ключ для спроса «гармошка» до паузы гармошек в СЧ. Сейчас все ключи НЧ требуют слово «складные», а 99% запросов СЧ-гармошек его не содержат (замечание ФЕНИКСА).</t>
-  </si>
-  <si>
-    <t>14.10: показы по новым фразам &gt; 0, CPC не выше 150 ₽</t>
+Сейчас фраза группы [складные] [перегородки] [гармошка] дала 7 кликов из 120, остальные 113 - автотаргетинг. Лиды пришли по «дверь гармошка на заказ», «перегородка гармошка», «межкомнатные перегородки гармошка». Фразы переводят этот спрос из автотаргетинга в управляемые ключи. Базовая «Складные» 5774336419 их не заберёт: у неё минус-слово «гармошка» на группе. Это и принимающий ключ перед паузой гармошек в СЧ.</t>
+  </si>
+  <si>
+    <t>14.10: клики по новым фразам &gt; 0, доля автотаргетинга в группе &lt; 70%, CPC ≤ 150 ₽</t>
   </si>
   <si>
     <t>5774336420</t>
@@ -1624,23 +1624,6 @@
   </si>
   <si>
     <t xml:space="preserve">РК № 712877525 [На заказ] Перегородки | Поиск НЧ | НБ=11т.р. | CPC=110 |
-Группа № 5774336419 - Складные перегородки</t>
-  </si>
-  <si>
-    <t>В фразе «[складные] [перегородки] -гармошка -заказ -зонирования -москве -стеклянные -цена» удалить минус-слова -заказ -цена -зонирования (оставить -гармошка -москве -стеклянные)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 233₽ / 52 кл / 5 лид / CPL 1 047 / отказ 33% / об.трафика 80 / премиум 64% / поз. 2,9
-Базовая группа с лучшим CPL семейства (5 лидов по меткам). Её подгруппы Заказ / Цена / Зонирования останавливаются, их запросы должны вернуться сюда.</t>
-  </si>
-  <si>
-    <t>14.10: клики базовой группы выросли, CPC не выше 130 ₽</t>
-  </si>
-  <si>
-    <t>5774336419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">РК № 712877525 [На заказ] Перегородки | Поиск НЧ | НБ=11т.р. | CPC=110 |
 Группа № 5774336430 - Стальные перегородки | Металлические Зонирования</t>
   </si>
   <si>
@@ -1651,22 +1634,18 @@
     <t>5774336430</t>
   </si>
   <si>
-    <t>7.10 (после правки фразы)</t>
-  </si>
-  <si>
     <t xml:space="preserve">РК № 712877525 [На заказ] Перегородки | Поиск НЧ | НБ=11т.р. | CPC=110 |
 Группа № 5774336417 - Складные перегородки | Заказ</t>
   </si>
   <si>
-    <t xml:space="preserve">ГЛУШИМ пауза
-(после правки фразы базовой группы 5774336419)</t>
+    <t>Выключить автотаргетинг в группе, фразу оставить (группу не останавливать)</t>
   </si>
   <si>
     <t xml:space="preserve">1 774₽ / 20 кл / 0 лид / отказ 25% / об.трафика 88 / премиум 79% / поз. 2,7
-Перехватывает запросы базовой группы, 0 лидов. Запросы вернутся в базовую группу без минус-слов.</t>
-  </si>
-  <si>
-    <t>14.10: базовая группа 5774336419 получает эти запросы</t>
+Фраза группы ни разу не сработала, все клики - автотаргетинг, и он приводит сюда общие запросы базовой группы («складная перегородка», «межкомнатные перегородки складные»): 0 лидов. Без автотаргетинга группа ловит только свои «заказ / цена», остальное уходит в базовую 5774336419 (5 лидов, CPL 1 047). Разделение сохраняется, фразу базовой группы не трогаем.</t>
+  </si>
+  <si>
+    <t>14.10: у группы расход ≈ 0 или только запросы с «заказ / цена»; клики базовой 5774336419 выросли</t>
   </si>
   <si>
     <t>5774336417</t>
@@ -1721,7 +1700,10 @@
   </si>
   <si>
     <t xml:space="preserve">579₽ / 12 кл / 0 лид / отказ 14% / об.трафика 80 / премиум 73% / поз. 2,7
-Перехватывает запросы базовой группы, 0 лидов. Запросы вернутся в базовую группу без минус-слов.</t>
+Интент «зонирование»: 12 кликов, 579 ₽, 0 лидов. По всем РК зонирование - худший кластер (CR 1,1%).</t>
+  </si>
+  <si>
+    <t>04.11: лиды семейства «Складные» не упали</t>
   </si>
   <si>
     <t>5774336418</t>
@@ -1732,7 +1714,7 @@
   </si>
   <si>
     <t xml:space="preserve">531₽ / 8 кл / 0 лид / отказ 0% / об.трафика 86 / премиум 84% / поз. 2,4
-Перехватывает запросы базовой группы, 0 лидов. Запросы вернутся в базовую группу без минус-слов.</t>
+Фраза группы ни разу не сработала, все клики - автотаргетинг, и он приводит сюда общие запросы базовой группы («складная перегородка», «межкомнатные перегородки складные»): 0 лидов. Без автотаргетинга группа ловит только свои «заказ / цена», остальное уходит в базовую 5774336419 (5 лидов, CPL 1 047). Разделение сохраняется, фразу базовой группы не трогаем.</t>
   </si>
   <si>
     <t>5774336421</t>
@@ -1760,8 +1742,15 @@
     <t>5774336407</t>
   </si>
   <si>
+    <t xml:space="preserve">РК № 712877525 [На заказ] Перегородки | Поиск НЧ | НБ=11т.р. | CPC=110 |
+Группа № 5774336419 - Складные перегородки</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 233₽ / 52 кл / 5 лид / CPL 1 047 / отказ 33% / об.трафика 80 / премиум 64% / поз. 2,9
 5 лида, CPL 1047 ₽ (среднее 3622 ₽), объём трафика 80 (цель 85+), премиум 64% показов, позиция 2.9. Повышаем только группы с 2+ лидами: у групп с 1 лидом данных мало.</t>
+  </si>
+  <si>
+    <t>5774336419</t>
   </si>
   <si>
     <t xml:space="preserve">РК № 712877525 [На заказ] Перегородки | Поиск НЧ | НБ=11т.р. | CPC=110 |
@@ -3335,7 +3324,7 @@
         <v>106</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -3344,13 +3333,13 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>91</v>
       </c>
       <c r="I4">
-        <v>8893</v>
+        <v>6588</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -10881,7 +10870,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S108"/>
+  <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -11086,16 +11075,16 @@
         <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>439</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>46</v>
@@ -11110,31 +11099,31 @@
         <v>2</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>453</v>
+        <v>48</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M4" s="3">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="N4" s="3">
-        <v>5233</v>
+        <v>1803</v>
       </c>
       <c r="O4" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="3">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="R4" s="3">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S4" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11148,13 +11137,13 @@
         <v>42</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>46</v>
@@ -11169,31 +11158,31 @@
         <v>2</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>48</v>
+        <v>456</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>457</v>
       </c>
       <c r="M5" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N5" s="3">
-        <v>1803</v>
+        <v>1774</v>
       </c>
       <c r="O5" s="3">
         <v>0</v>
       </c>
       <c r="P5" s="3">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="Q5" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R5" s="3">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S5" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11204,16 +11193,16 @@
         <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>46</v>
@@ -11228,31 +11217,31 @@
         <v>2</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>462</v>
+        <v>48</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M6" s="3">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="N6" s="3">
-        <v>1774</v>
+        <v>1338</v>
       </c>
       <c r="O6" s="3">
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="3">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="R6" s="3">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="S6" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11266,13 +11255,13 @@
         <v>42</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>46</v>
@@ -11290,25 +11279,25 @@
         <v>48</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="M7" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N7" s="3">
-        <v>1338</v>
+        <v>760</v>
       </c>
       <c r="O7" s="3">
         <v>0</v>
       </c>
       <c r="P7" s="3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Q7" s="3">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="R7" s="3">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="S7" s="3">
         <v>0</v>
@@ -11325,13 +11314,13 @@
         <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>46</v>
@@ -11349,25 +11338,25 @@
         <v>48</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M8" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N8" s="3">
-        <v>760</v>
+        <v>609</v>
       </c>
       <c r="O8" s="3">
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="3">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="R8" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S8" s="3">
         <v>0</v>
@@ -11384,13 +11373,13 @@
         <v>42</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>46</v>
@@ -11408,28 +11397,28 @@
         <v>48</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M9" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" s="3">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
       </c>
       <c r="P9" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="Q9" s="3">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R9" s="3">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11443,13 +11432,13 @@
         <v>42</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>46</v>
@@ -11464,31 +11453,31 @@
         <v>2</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>48</v>
+        <v>472</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M10" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N10" s="3">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="O10" s="3">
         <v>0</v>
       </c>
       <c r="P10" s="3">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="Q10" s="3">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="R10" s="3">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="S10" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11499,16 +11488,16 @@
         <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>458</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>460</v>
+        <v>474</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>454</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>46</v>
@@ -11523,31 +11512,31 @@
         <v>2</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M11" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N11" s="3">
-        <v>579</v>
+        <v>531</v>
       </c>
       <c r="O11" s="3">
         <v>0</v>
       </c>
       <c r="P11" s="3">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="Q11" s="3">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="R11" s="3">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S11" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11558,16 +11547,16 @@
         <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>458</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>460</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>46</v>
@@ -11582,31 +11571,31 @@
         <v>2</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>462</v>
+        <v>48</v>
       </c>
       <c r="L12" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="M12" s="3">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>481</v>
       </c>
-      <c r="M12" s="3">
-        <v>8</v>
-      </c>
-      <c r="N12" s="3">
-        <v>531</v>
-      </c>
       <c r="O12" s="3">
         <v>0</v>
       </c>
       <c r="P12" s="3">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="Q12" s="3">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="R12" s="3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S12" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11620,13 +11609,13 @@
         <v>42</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>46</v>
@@ -11644,28 +11633,28 @@
         <v>48</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M13" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N13" s="3">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="O13" s="3">
         <v>0</v>
       </c>
       <c r="P13" s="3">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="Q13" s="3">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="R13" s="3">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S13" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11679,13 +11668,13 @@
         <v>42</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>44</v>
+        <v>483</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>335</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>46</v>
@@ -11697,34 +11686,34 @@
         <v>40</v>
       </c>
       <c r="J14" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>48</v>
+        <v>333</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M14" s="3">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="N14" s="3">
-        <v>432</v>
+        <v>5233</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P14" s="3">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="Q14" s="3">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="R14" s="3">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="S14" s="3">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11738,13 +11727,13 @@
         <v>42</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>450</v>
+        <v>486</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>335</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>46</v>
@@ -11762,28 +11751,28 @@
         <v>333</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>454</v>
+        <v>488</v>
       </c>
       <c r="M15" s="3">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="N15" s="3">
-        <v>5233</v>
+        <v>2198</v>
       </c>
       <c r="O15" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P15" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="3">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="R15" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S15" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11824,25 +11813,25 @@
         <v>491</v>
       </c>
       <c r="M16" s="3">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="N16" s="3">
-        <v>2198</v>
+        <v>1852</v>
       </c>
       <c r="O16" s="3">
         <v>2</v>
       </c>
       <c r="P16" s="3">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="Q16" s="3">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R16" s="3">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="S16" s="3">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11853,55 +11842,55 @@
         <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>335</v>
+      <c r="E17" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>493</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J17" s="3">
-        <v>3</v>
+      <c r="J17" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>494</v>
       </c>
       <c r="M17" s="3">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N17" s="3">
-        <v>1852</v>
+        <v>2926</v>
       </c>
       <c r="O17" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="3">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q17" s="3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="R17" s="3">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="S17" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11936,31 +11925,31 @@
         <v>99</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M18" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N18" s="3">
-        <v>2926</v>
+        <v>2551</v>
       </c>
       <c r="O18" s="3">
         <v>0</v>
       </c>
       <c r="P18" s="3">
+        <v>78</v>
+      </c>
+      <c r="Q18" s="3">
         <v>85</v>
       </c>
-      <c r="Q18" s="3">
-        <v>75</v>
-      </c>
       <c r="R18" s="3">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="S18" s="3">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11974,13 +11963,13 @@
         <v>40</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>97</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>40</v>
@@ -11995,31 +11984,31 @@
         <v>99</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>501</v>
       </c>
       <c r="M19" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="N19" s="3">
-        <v>2551</v>
+        <v>2198</v>
       </c>
       <c r="O19" s="3">
         <v>0</v>
       </c>
       <c r="P19" s="3">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q19" s="3">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="R19" s="3">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="S19" s="3">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12054,31 +12043,31 @@
         <v>99</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>504</v>
       </c>
       <c r="M20" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="N20" s="3">
-        <v>2198</v>
+        <v>2126</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="Q20" s="3">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="R20" s="3">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="S20" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12113,31 +12102,31 @@
         <v>99</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>507</v>
       </c>
       <c r="M21" s="3">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N21" s="3">
-        <v>2126</v>
+        <v>1801</v>
       </c>
       <c r="O21" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="3">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="Q21" s="3">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="R21" s="3">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="S21" s="3">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12178,25 +12167,25 @@
         <v>510</v>
       </c>
       <c r="M22" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N22" s="3">
-        <v>1801</v>
+        <v>1750</v>
       </c>
       <c r="O22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P22" s="3">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="Q22" s="3">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="R22" s="3">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="S22" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12231,31 +12220,31 @@
         <v>99</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>513</v>
       </c>
       <c r="M23" s="3">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N23" s="3">
-        <v>1750</v>
+        <v>1743</v>
       </c>
       <c r="O23" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="Q23" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R23" s="3">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="S23" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12290,31 +12279,31 @@
         <v>99</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>516</v>
       </c>
       <c r="M24" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="N24" s="3">
-        <v>1743</v>
+        <v>1734</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" s="3">
         <v>87</v>
       </c>
       <c r="Q24" s="3">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="R24" s="3">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12349,31 +12338,31 @@
         <v>99</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>519</v>
       </c>
       <c r="M25" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N25" s="3">
-        <v>1734</v>
+        <v>1543</v>
       </c>
       <c r="O25" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="3">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q25" s="3">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="R25" s="3">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S25" s="3">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12408,31 +12397,31 @@
         <v>99</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>522</v>
       </c>
       <c r="M26" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N26" s="3">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="O26" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" s="3">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="Q26" s="3">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="R26" s="3">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S26" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12473,10 +12462,10 @@
         <v>525</v>
       </c>
       <c r="M27" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N27" s="3">
-        <v>1541</v>
+        <v>1448</v>
       </c>
       <c r="O27" s="3">
         <v>1</v>
@@ -12485,13 +12474,13 @@
         <v>78</v>
       </c>
       <c r="Q27" s="3">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="R27" s="3">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="S27" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12532,25 +12521,25 @@
         <v>528</v>
       </c>
       <c r="M28" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N28" s="3">
-        <v>1448</v>
+        <v>1313</v>
       </c>
       <c r="O28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q28" s="3">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="R28" s="3">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="S28" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12585,31 +12574,31 @@
         <v>99</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>531</v>
       </c>
       <c r="M29" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N29" s="3">
-        <v>1313</v>
+        <v>1257</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="Q29" s="3">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="R29" s="3">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S29" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12644,31 +12633,31 @@
         <v>99</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>534</v>
       </c>
       <c r="M30" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N30" s="3">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="O30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="3">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="Q30" s="3">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="R30" s="3">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="S30" s="3">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12703,31 +12692,31 @@
         <v>99</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L31" s="3" t="s">
         <v>537</v>
       </c>
       <c r="M31" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N31" s="3">
-        <v>1252</v>
+        <v>1136</v>
       </c>
       <c r="O31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q31" s="3">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="R31" s="3">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S31" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12762,31 +12751,31 @@
         <v>99</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>540</v>
       </c>
       <c r="M32" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N32" s="3">
-        <v>1136</v>
+        <v>1088</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="Q32" s="3">
         <v>56</v>
       </c>
       <c r="R32" s="3">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="S32" s="3">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12821,31 +12810,31 @@
         <v>99</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L33" s="3" t="s">
         <v>543</v>
       </c>
       <c r="M33" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N33" s="3">
-        <v>1088</v>
+        <v>991</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="Q33" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="R33" s="3">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="S33" s="3">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12880,31 +12869,31 @@
         <v>99</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L34" s="3" t="s">
         <v>546</v>
       </c>
       <c r="M34" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N34" s="3">
-        <v>991</v>
+        <v>964</v>
       </c>
       <c r="O34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" s="3">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="Q34" s="3">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="R34" s="3">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S34" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12945,25 +12934,25 @@
         <v>549</v>
       </c>
       <c r="M35" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N35" s="3">
-        <v>964</v>
+        <v>857</v>
       </c>
       <c r="O35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="Q35" s="3">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="R35" s="3">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13004,25 +12993,25 @@
         <v>552</v>
       </c>
       <c r="M36" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N36" s="3">
-        <v>857</v>
+        <v>828</v>
       </c>
       <c r="O36" s="3">
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="Q36" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="R36" s="3">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="S36" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13057,31 +13046,31 @@
         <v>99</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L37" s="3" t="s">
         <v>555</v>
       </c>
       <c r="M37" s="3">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="N37" s="3">
-        <v>828</v>
+        <v>817</v>
       </c>
       <c r="O37" s="3">
         <v>0</v>
       </c>
       <c r="P37" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="Q37" s="3">
         <v>64</v>
       </c>
       <c r="R37" s="3">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="S37" s="3">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13116,7 +13105,7 @@
         <v>99</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>558</v>
@@ -13128,19 +13117,19 @@
         <v>817</v>
       </c>
       <c r="O38" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" s="3">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="Q38" s="3">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="R38" s="3">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="S38" s="3">
-        <v>80</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13181,25 +13170,25 @@
         <v>561</v>
       </c>
       <c r="M39" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N39" s="3">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="O39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" s="3">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q39" s="3">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="R39" s="3">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="S39" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13234,7 +13223,7 @@
         <v>99</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L40" s="3" t="s">
         <v>564</v>
@@ -13243,19 +13232,19 @@
         <v>5</v>
       </c>
       <c r="N40" s="3">
-        <v>802</v>
+        <v>766</v>
       </c>
       <c r="O40" s="3">
         <v>0</v>
       </c>
       <c r="P40" s="3">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="Q40" s="3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R40" s="3">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="S40" s="3">
         <v>0</v>
@@ -13293,28 +13282,28 @@
         <v>99</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>567</v>
       </c>
       <c r="M41" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N41" s="3">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q41" s="3">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="R41" s="3">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="S41" s="3">
         <v>0</v>
@@ -13352,31 +13341,31 @@
         <v>99</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>570</v>
       </c>
       <c r="M42" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N42" s="3">
-        <v>748</v>
+        <v>728</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="Q42" s="3">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="R42" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13411,31 +13400,31 @@
         <v>99</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>573</v>
       </c>
       <c r="M43" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N43" s="3">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="Q43" s="3">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="R43" s="3">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="S43" s="3">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13470,31 +13459,31 @@
         <v>99</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>576</v>
       </c>
       <c r="M44" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N44" s="3">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q44" s="3">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="R44" s="3">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="S44" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13529,28 +13518,28 @@
         <v>99</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>579</v>
       </c>
       <c r="M45" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45" s="3">
-        <v>706</v>
+        <v>684</v>
       </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
       <c r="P45" s="3">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="Q45" s="3">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="R45" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S45" s="3">
         <v>0</v>
@@ -13594,22 +13583,22 @@
         <v>582</v>
       </c>
       <c r="M46" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N46" s="3">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="O46" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" s="3">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="Q46" s="3">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="R46" s="3">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="S46" s="3">
         <v>0</v>
@@ -13653,25 +13642,25 @@
         <v>585</v>
       </c>
       <c r="M47" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N47" s="3">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="O47" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47" s="3">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="Q47" s="3">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R47" s="3">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S47" s="3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13712,25 +13701,25 @@
         <v>588</v>
       </c>
       <c r="M48" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N48" s="3">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
       </c>
       <c r="P48" s="3">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q48" s="3">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="R48" s="3">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="S48" s="3">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13765,31 +13754,31 @@
         <v>99</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>591</v>
       </c>
       <c r="M49" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N49" s="3">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
       <c r="P49" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q49" s="3">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="R49" s="3">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="S49" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13824,7 +13813,7 @@
         <v>99</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L50" s="3" t="s">
         <v>594</v>
@@ -13833,19 +13822,19 @@
         <v>3</v>
       </c>
       <c r="N50" s="3">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="O50" s="3">
         <v>0</v>
       </c>
       <c r="P50" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q50" s="3">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="R50" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="S50" s="3">
         <v>0</v>
@@ -13883,31 +13872,31 @@
         <v>99</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>597</v>
       </c>
       <c r="M51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51" s="3">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="O51" s="3">
         <v>0</v>
       </c>
       <c r="P51" s="3">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="Q51" s="3">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="R51" s="3">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="S51" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13942,7 +13931,7 @@
         <v>99</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>600</v>
@@ -13951,22 +13940,22 @@
         <v>6</v>
       </c>
       <c r="N52" s="3">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
       </c>
       <c r="P52" s="3">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="Q52" s="3">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="R52" s="3">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="S52" s="3">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14001,31 +13990,31 @@
         <v>99</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L53" s="3" t="s">
         <v>603</v>
       </c>
       <c r="M53" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53" s="3">
-        <v>598</v>
+        <v>545</v>
       </c>
       <c r="O53" s="3">
         <v>0</v>
       </c>
       <c r="P53" s="3">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q53" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R53" s="3">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="S53" s="3">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14060,7 +14049,7 @@
         <v>99</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>606</v>
@@ -14069,22 +14058,22 @@
         <v>5</v>
       </c>
       <c r="N54" s="3">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="O54" s="3">
         <v>0</v>
       </c>
       <c r="P54" s="3">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="Q54" s="3">
         <v>59</v>
       </c>
       <c r="R54" s="3">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="S54" s="3">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14125,25 +14114,25 @@
         <v>609</v>
       </c>
       <c r="M55" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N55" s="3">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="O55" s="3">
         <v>0</v>
       </c>
       <c r="P55" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q55" s="3">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="R55" s="3">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="S55" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14178,31 +14167,31 @@
         <v>99</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>612</v>
       </c>
       <c r="M56" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N56" s="3">
-        <v>519</v>
+        <v>497</v>
       </c>
       <c r="O56" s="3">
         <v>0</v>
       </c>
       <c r="P56" s="3">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="Q56" s="3">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="R56" s="3">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="S56" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14237,7 +14226,7 @@
         <v>99</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>615</v>
@@ -14246,22 +14235,22 @@
         <v>3</v>
       </c>
       <c r="N57" s="3">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57" s="3">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q57" s="3">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="R57" s="3">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14296,31 +14285,31 @@
         <v>99</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>618</v>
       </c>
       <c r="M58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N58" s="3">
-        <v>483</v>
+        <v>439</v>
       </c>
       <c r="O58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="Q58" s="3">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="R58" s="3">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="S58" s="3">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14355,31 +14344,31 @@
         <v>99</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>621</v>
       </c>
       <c r="M59" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N59" s="3">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="O59" s="3">
         <v>0</v>
       </c>
       <c r="P59" s="3">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="Q59" s="3">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="R59" s="3">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="S59" s="3">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14414,31 +14403,31 @@
         <v>99</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>624</v>
       </c>
       <c r="M60" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N60" s="3">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="O60" s="3">
         <v>0</v>
       </c>
       <c r="P60" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q60" s="3">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="R60" s="3">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="S60" s="3">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14473,31 +14462,31 @@
         <v>99</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>627</v>
       </c>
       <c r="M61" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N61" s="3">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q61" s="3">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="R61" s="3">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="S61" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14538,25 +14527,25 @@
         <v>630</v>
       </c>
       <c r="M62" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="N62" s="3">
-        <v>348</v>
+        <v>326</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
       </c>
       <c r="P62" s="3">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="Q62" s="3">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="R62" s="3">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="S62" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14600,22 +14589,22 @@
         <v>2</v>
       </c>
       <c r="N63" s="3">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="O63" s="3">
         <v>0</v>
       </c>
       <c r="P63" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="Q63" s="3">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="R63" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14656,22 +14645,22 @@
         <v>636</v>
       </c>
       <c r="M64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N64" s="3">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="O64" s="3">
         <v>0</v>
       </c>
       <c r="P64" s="3">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="Q64" s="3">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="R64" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S64" s="3">
         <v>0</v>
@@ -14715,22 +14704,22 @@
         <v>639</v>
       </c>
       <c r="M65" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N65" s="3">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="O65" s="3">
         <v>0</v>
       </c>
       <c r="P65" s="3">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Q65" s="3">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="R65" s="3">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="S65" s="3">
         <v>0</v>
@@ -14768,28 +14757,28 @@
         <v>99</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>642</v>
       </c>
       <c r="M66" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" s="3">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="O66" s="3">
         <v>0</v>
       </c>
       <c r="P66" s="3">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="Q66" s="3">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="R66" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S66" s="3">
         <v>0</v>
@@ -14827,31 +14816,31 @@
         <v>99</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>645</v>
       </c>
       <c r="M67" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N67" s="3">
-        <v>234</v>
+        <v>129</v>
       </c>
       <c r="O67" s="3">
         <v>0</v>
       </c>
       <c r="P67" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="Q67" s="3">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="R67" s="3">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="S67" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14886,31 +14875,31 @@
         <v>99</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>648</v>
       </c>
       <c r="M68" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68" s="3">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="O68" s="3">
         <v>0</v>
       </c>
       <c r="P68" s="3">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="Q68" s="3">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="R68" s="3">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="S68" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14945,7 +14934,7 @@
         <v>99</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>651</v>
@@ -14954,22 +14943,22 @@
         <v>2</v>
       </c>
       <c r="N69" s="3">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="O69" s="3">
         <v>0</v>
       </c>
       <c r="P69" s="3">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="Q69" s="3">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="R69" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="S69" s="3">
-        <v>0</v>
+        <v>1.5</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15004,13 +14993,13 @@
         <v>99</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>654</v>
       </c>
       <c r="M70" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="3">
         <v>107</v>
@@ -15019,16 +15008,16 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="Q70" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R70" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>40</v>
+        <v>1.9</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15072,19 +15061,19 @@
         <v>1</v>
       </c>
       <c r="N71" s="3">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="O71" s="3">
         <v>0</v>
       </c>
       <c r="P71" s="3">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="Q71" s="3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R71" s="3">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="S71" s="3">
         <v>0</v>
@@ -15128,22 +15117,22 @@
         <v>660</v>
       </c>
       <c r="M72" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N72" s="3">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="O72" s="3">
         <v>0</v>
       </c>
       <c r="P72" s="3">
+        <v>86</v>
+      </c>
+      <c r="Q72" s="3">
         <v>76</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="S72" s="3">
         <v>0</v>
@@ -15181,7 +15170,7 @@
         <v>99</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>663</v>
@@ -15190,7 +15179,7 @@
         <v>2</v>
       </c>
       <c r="N73" s="3">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O73" s="3">
         <v>0</v>
@@ -15199,10 +15188,10 @@
         <v>86</v>
       </c>
       <c r="Q73" s="3">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="R73" s="3">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S73" s="3">
         <v>0</v>
@@ -15240,31 +15229,31 @@
         <v>99</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>666</v>
       </c>
       <c r="M74" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N74" s="3">
+        <v>48</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>88</v>
+      </c>
+      <c r="Q74" s="3">
         <v>62</v>
       </c>
-      <c r="O74" s="3">
-        <v>0</v>
-      </c>
-      <c r="P74" s="3">
-        <v>86</v>
-      </c>
-      <c r="Q74" s="3">
-        <v>66</v>
-      </c>
       <c r="R74" s="3">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="S74" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15299,7 +15288,7 @@
         <v>99</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>100</v>
+        <v>497</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>669</v>
@@ -15308,19 +15297,19 @@
         <v>1</v>
       </c>
       <c r="N75" s="3">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="O75" s="3">
         <v>0</v>
       </c>
       <c r="P75" s="3">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="Q75" s="3">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="R75" s="3">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="S75" s="3">
         <v>100</v>
@@ -15358,7 +15347,7 @@
         <v>99</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>672</v>
@@ -15367,22 +15356,22 @@
         <v>1</v>
       </c>
       <c r="N76" s="3">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="O76" s="3">
         <v>0</v>
       </c>
       <c r="P76" s="3">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="Q76" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R76" s="3">
-        <v>3.8</v>
-      </c>
-      <c r="S76" s="3">
-        <v>100</v>
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="77" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15417,28 +15406,28 @@
         <v>99</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>675</v>
       </c>
       <c r="M77" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O77" s="3">
         <v>0</v>
       </c>
       <c r="P77" s="3">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="Q77" s="3">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="R77" s="3">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="S77" s="3" t="s">
         <v>40</v>
@@ -15491,13 +15480,13 @@
         <v>0</v>
       </c>
       <c r="P78" s="3">
-        <v>82</v>
+        <v>27</v>
       </c>
       <c r="Q78" s="3">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="R78" s="3">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="S78" s="3" t="s">
         <v>40</v>
@@ -15550,13 +15539,13 @@
         <v>0</v>
       </c>
       <c r="P79" s="3">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="Q79" s="3">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="R79" s="3">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="S79" s="3" t="s">
         <v>40</v>
@@ -15579,7 +15568,7 @@
         <v>97</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>683</v>
+        <v>244</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>40</v>
@@ -15597,7 +15586,7 @@
         <v>100</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="M80" s="3">
         <v>0</v>
@@ -15608,14 +15597,14 @@
       <c r="O80" s="3">
         <v>0</v>
       </c>
-      <c r="P80" s="3">
-        <v>117</v>
-      </c>
-      <c r="Q80" s="3">
-        <v>67</v>
-      </c>
-      <c r="R80" s="3">
-        <v>2.3</v>
+      <c r="P80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q80" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R80" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="S80" s="3" t="s">
         <v>40</v>
@@ -15632,13 +15621,13 @@
         <v>40</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>97</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>244</v>
+        <v>685</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>40</v>
@@ -15667,14 +15656,14 @@
       <c r="O81" s="3">
         <v>0</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>40</v>
+      <c r="P81" s="3">
+        <v>72</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
+        <v>1</v>
       </c>
       <c r="S81" s="3" t="s">
         <v>40</v>
@@ -15727,13 +15716,13 @@
         <v>0</v>
       </c>
       <c r="P82" s="3">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="Q82" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R82" s="3">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S82" s="3" t="s">
         <v>40</v>
@@ -15786,13 +15775,13 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R83" s="3">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>40</v>
@@ -15845,7 +15834,7 @@
         <v>0</v>
       </c>
       <c r="P84" s="3">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="Q84" s="3">
         <v>0</v>
@@ -15904,13 +15893,13 @@
         <v>0</v>
       </c>
       <c r="P85" s="3">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="Q85" s="3">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R85" s="3">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S85" s="3" t="s">
         <v>40</v>
@@ -15963,13 +15952,13 @@
         <v>0</v>
       </c>
       <c r="P86" s="3">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="Q86" s="3">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="R86" s="3">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="S86" s="3" t="s">
         <v>40</v>
@@ -16022,13 +16011,13 @@
         <v>0</v>
       </c>
       <c r="P87" s="3">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q87" s="3">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="R87" s="3">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="S87" s="3" t="s">
         <v>40</v>
@@ -16081,13 +16070,13 @@
         <v>0</v>
       </c>
       <c r="P88" s="3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="Q88" s="3">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="R88" s="3">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="S88" s="3" t="s">
         <v>40</v>
@@ -16140,13 +16129,13 @@
         <v>0</v>
       </c>
       <c r="P89" s="3">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="Q89" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>40</v>
@@ -16199,13 +16188,13 @@
         <v>0</v>
       </c>
       <c r="P90" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q90" s="3">
         <v>42</v>
       </c>
-      <c r="Q90" s="3">
-        <v>0</v>
-      </c>
       <c r="R90" s="3">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="S90" s="3" t="s">
         <v>40</v>
@@ -16258,13 +16247,13 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q91" s="3">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="R91" s="3">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>40</v>
@@ -16317,13 +16306,13 @@
         <v>0</v>
       </c>
       <c r="P92" s="3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q92" s="3">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="R92" s="3">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="S92" s="3" t="s">
         <v>40</v>
@@ -16376,13 +16365,13 @@
         <v>0</v>
       </c>
       <c r="P93" s="3">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="Q93" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R93" s="3">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="S93" s="3" t="s">
         <v>40</v>
@@ -16435,13 +16424,13 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="Q94" s="3">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="R94" s="3">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>40</v>
@@ -16494,10 +16483,10 @@
         <v>0</v>
       </c>
       <c r="P95" s="3">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="Q95" s="3">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="R95" s="3">
         <v>3.3</v>
@@ -16553,13 +16542,13 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="Q96" s="3">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="R96" s="3">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="S96" s="3" t="s">
         <v>40</v>
@@ -16612,13 +16601,13 @@
         <v>0</v>
       </c>
       <c r="P97" s="3">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="Q97" s="3">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="R97" s="3">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="S97" s="3" t="s">
         <v>40</v>
@@ -16671,13 +16660,13 @@
         <v>0</v>
       </c>
       <c r="P98" s="3">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="Q98" s="3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="R98" s="3">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S98" s="3" t="s">
         <v>40</v>
@@ -16730,10 +16719,10 @@
         <v>0</v>
       </c>
       <c r="P99" s="3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="Q99" s="3">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="R99" s="3">
         <v>2.1</v>
@@ -16759,7 +16748,7 @@
         <v>97</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>742</v>
+        <v>244</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>40</v>
@@ -16777,7 +16766,7 @@
         <v>100</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -16788,14 +16777,14 @@
       <c r="O100" s="3">
         <v>0</v>
       </c>
-      <c r="P100" s="3">
-        <v>81</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>38</v>
-      </c>
-      <c r="R100" s="3">
-        <v>2.1</v>
+      <c r="P100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>40</v>
@@ -16812,13 +16801,13 @@
         <v>40</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>97</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>244</v>
+        <v>744</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>40</v>
@@ -16847,14 +16836,14 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>40</v>
+      <c r="P101" s="3">
+        <v>61</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>25</v>
+      </c>
+      <c r="R101" s="3">
+        <v>3</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>40</v>
@@ -16907,13 +16896,13 @@
         <v>0</v>
       </c>
       <c r="P102" s="3">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="Q102" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R102" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>40</v>
@@ -16966,13 +16955,13 @@
         <v>0</v>
       </c>
       <c r="P103" s="3">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="Q103" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R103" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S103" s="3" t="s">
         <v>40</v>
@@ -16995,7 +16984,7 @@
         <v>97</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>753</v>
+        <v>244</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>40</v>
@@ -17013,7 +17002,7 @@
         <v>100</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="M104" s="3">
         <v>0</v>
@@ -17024,14 +17013,14 @@
       <c r="O104" s="3">
         <v>0</v>
       </c>
-      <c r="P104" s="3">
-        <v>55</v>
-      </c>
-      <c r="Q104" s="3">
-        <v>0</v>
-      </c>
-      <c r="R104" s="3">
-        <v>1</v>
+      <c r="P104" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q104" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R104" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="S104" s="3" t="s">
         <v>40</v>
@@ -17048,13 +17037,13 @@
         <v>40</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>97</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>244</v>
+        <v>755</v>
       </c>
       <c r="G105" s="3" t="s">
         <v>40</v>
@@ -17083,14 +17072,14 @@
       <c r="O105" s="3">
         <v>0</v>
       </c>
-      <c r="P105" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q105" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R105" s="3" t="s">
-        <v>40</v>
+      <c r="P105" s="3">
+        <v>79</v>
+      </c>
+      <c r="Q105" s="3">
+        <v>79</v>
+      </c>
+      <c r="R105" s="3">
+        <v>3.1</v>
       </c>
       <c r="S105" s="3" t="s">
         <v>40</v>
@@ -17143,13 +17132,13 @@
         <v>0</v>
       </c>
       <c r="P106" s="3">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="Q106" s="3">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="R106" s="3">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="S106" s="3" t="s">
         <v>40</v>
@@ -17202,74 +17191,15 @@
         <v>0</v>
       </c>
       <c r="P107" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q107" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R107" s="3">
-        <v>5.5</v>
+        <v>1.9</v>
       </c>
       <c r="S107" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="E108" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J108" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K108" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L108" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="M108" s="3">
-        <v>0</v>
-      </c>
-      <c r="N108" s="3">
-        <v>0</v>
-      </c>
-      <c r="O108" s="3">
-        <v>0</v>
-      </c>
-      <c r="P108" s="3">
-        <v>72</v>
-      </c>
-      <c r="Q108" s="3">
-        <v>29</v>
-      </c>
-      <c r="R108" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="S108" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -17282,7 +17212,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S55"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -18313,16 +18243,16 @@
         <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>439</v>
+        <v>305</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>451</v>
+        <v>316</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>307</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>452</v>
+        <v>317</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>46</v>
@@ -18337,31 +18267,31 @@
         <v>2</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>453</v>
+        <v>309</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>454</v>
+        <v>318</v>
       </c>
       <c r="M18" s="3">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="N18" s="3">
-        <v>5233</v>
+        <v>3936</v>
       </c>
       <c r="O18" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P18" s="3">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Q18" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="R18" s="3">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="S18" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18375,13 +18305,13 @@
         <v>305</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>307</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>46</v>
@@ -18399,28 +18329,28 @@
         <v>309</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M19" s="3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="N19" s="3">
-        <v>3936</v>
+        <v>3892</v>
       </c>
       <c r="O19" s="3">
         <v>1</v>
       </c>
       <c r="P19" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="3">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="R19" s="3">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="S19" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18431,16 +18361,16 @@
         <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>305</v>
+        <v>42</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>319</v>
+        <v>43</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>320</v>
+        <v>45</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>46</v>
@@ -18455,31 +18385,31 @@
         <v>2</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>309</v>
+        <v>48</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>321</v>
+        <v>49</v>
       </c>
       <c r="M20" s="3">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="N20" s="3">
-        <v>3892</v>
+        <v>3870</v>
       </c>
       <c r="O20" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="Q20" s="3">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="R20" s="3">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="S20" s="3">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18490,16 +18420,16 @@
         <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>46</v>
@@ -18514,31 +18444,31 @@
         <v>2</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M21" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="N21" s="3">
-        <v>3870</v>
+        <v>2998</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
       <c r="P21" s="3">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="Q21" s="3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="R21" s="3">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="S21" s="3">
-        <v>15</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18552,13 +18482,13 @@
         <v>50</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>46</v>
@@ -18576,28 +18506,28 @@
         <v>54</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M22" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="N22" s="3">
-        <v>2998</v>
+        <v>2468</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q22" s="3">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="R22" s="3">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="S22" s="3">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18608,16 +18538,16 @@
         <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>50</v>
+        <v>305</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>56</v>
+        <v>322</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>52</v>
+        <v>307</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>57</v>
+        <v>323</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>46</v>
@@ -18632,31 +18562,31 @@
         <v>2</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>54</v>
+        <v>309</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>58</v>
+        <v>324</v>
       </c>
       <c r="M23" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N23" s="3">
-        <v>2468</v>
+        <v>2042</v>
       </c>
       <c r="O23" s="3">
         <v>0</v>
       </c>
       <c r="P23" s="3">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="Q23" s="3">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="R23" s="3">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="S23" s="3">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18667,16 +18597,16 @@
         <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>305</v>
+        <v>42</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>322</v>
+        <v>450</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>323</v>
+        <v>451</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>46</v>
@@ -18691,31 +18621,31 @@
         <v>2</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>309</v>
+        <v>48</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>324</v>
+        <v>452</v>
       </c>
       <c r="M24" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N24" s="3">
-        <v>2042</v>
+        <v>1803</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="Q24" s="3">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="R24" s="3">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S24" s="3">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18729,13 +18659,13 @@
         <v>42</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>46</v>
@@ -18750,31 +18680,31 @@
         <v>2</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>48</v>
+        <v>456</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>457</v>
       </c>
       <c r="M25" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N25" s="3">
-        <v>1803</v>
+        <v>1774</v>
       </c>
       <c r="O25" s="3">
         <v>0</v>
       </c>
       <c r="P25" s="3">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="Q25" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R25" s="3">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="S25" s="3">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18785,16 +18715,16 @@
         <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>458</v>
+        <v>42</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>459</v>
+        <v>59</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>460</v>
+        <v>44</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>461</v>
+        <v>60</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>46</v>
@@ -18809,31 +18739,31 @@
         <v>2</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>462</v>
+        <v>48</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>463</v>
+        <v>61</v>
       </c>
       <c r="M26" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N26" s="3">
-        <v>1774</v>
+        <v>1650</v>
       </c>
       <c r="O26" s="3">
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="Q26" s="3">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="R26" s="3">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="S26" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18844,16 +18774,16 @@
         <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>42</v>
+        <v>305</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
+        <v>325</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>44</v>
+        <v>307</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>60</v>
+        <v>326</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>46</v>
@@ -18868,31 +18798,31 @@
         <v>2</v>
       </c>
       <c r="K27" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="M27" s="3">
+        <v>19</v>
+      </c>
+      <c r="N27" s="3">
+        <v>1501</v>
+      </c>
+      <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
+        <v>87</v>
+      </c>
+      <c r="Q27" s="3">
         <v>48</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="M27" s="3">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
-        <v>1650</v>
-      </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>61</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>87</v>
-      </c>
       <c r="R27" s="3">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="S27" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18906,13 +18836,13 @@
         <v>305</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>307</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>46</v>
@@ -18930,28 +18860,28 @@
         <v>309</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="M28" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N28" s="3">
-        <v>1501</v>
+        <v>1406</v>
       </c>
       <c r="O28" s="3">
         <v>0</v>
       </c>
       <c r="P28" s="3">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="Q28" s="3">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="R28" s="3">
         <v>2.2</v>
       </c>
       <c r="S28" s="3">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18962,16 +18892,16 @@
         <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>305</v>
+        <v>42</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>328</v>
+        <v>458</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>307</v>
+        <v>44</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>329</v>
+        <v>459</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>46</v>
@@ -18986,31 +18916,31 @@
         <v>2</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>309</v>
+        <v>48</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>330</v>
+        <v>460</v>
       </c>
       <c r="M29" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N29" s="3">
-        <v>1406</v>
+        <v>1338</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="Q29" s="3">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="R29" s="3">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="S29" s="3">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19021,16 +18951,16 @@
         <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>464</v>
+        <v>62</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>465</v>
+        <v>63</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>46</v>
@@ -19045,31 +18975,31 @@
         <v>2</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>466</v>
+        <v>64</v>
       </c>
       <c r="M30" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="N30" s="3">
-        <v>1338</v>
+        <v>1191</v>
       </c>
       <c r="O30" s="3">
         <v>0</v>
       </c>
       <c r="P30" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="Q30" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="R30" s="3">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="S30" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19083,13 +19013,13 @@
         <v>50</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>46</v>
@@ -19107,28 +19037,28 @@
         <v>54</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M31" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N31" s="3">
-        <v>1191</v>
+        <v>965</v>
       </c>
       <c r="O31" s="3">
         <v>0</v>
       </c>
       <c r="P31" s="3">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="Q31" s="3">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="R31" s="3">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="S31" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19142,13 +19072,13 @@
         <v>50</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>46</v>
@@ -19166,25 +19096,25 @@
         <v>54</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M32" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N32" s="3">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="Q32" s="3">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="R32" s="3">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="S32" s="3">
         <v>0</v>
@@ -19198,16 +19128,16 @@
         <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>68</v>
+        <v>461</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>69</v>
+        <v>462</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>46</v>
@@ -19222,28 +19152,28 @@
         <v>2</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>70</v>
+        <v>463</v>
       </c>
       <c r="M33" s="3">
         <v>5</v>
       </c>
       <c r="N33" s="3">
-        <v>949</v>
+        <v>760</v>
       </c>
       <c r="O33" s="3">
         <v>0</v>
       </c>
       <c r="P33" s="3">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q33" s="3">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="R33" s="3">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="S33" s="3">
         <v>0</v>
@@ -19260,13 +19190,13 @@
         <v>42</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>46</v>
@@ -19284,25 +19214,25 @@
         <v>48</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M34" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N34" s="3">
-        <v>760</v>
+        <v>609</v>
       </c>
       <c r="O34" s="3">
         <v>0</v>
       </c>
       <c r="P34" s="3">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q34" s="3">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="R34" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S34" s="3">
         <v>0</v>
@@ -19319,13 +19249,13 @@
         <v>42</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>46</v>
@@ -19343,28 +19273,28 @@
         <v>48</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M35" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N35" s="3">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="O35" s="3">
         <v>0</v>
       </c>
       <c r="P35" s="3">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="Q35" s="3">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R35" s="3">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S35" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19378,13 +19308,13 @@
         <v>42</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>46</v>
@@ -19399,31 +19329,31 @@
         <v>2</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>48</v>
+        <v>472</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="M36" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="N36" s="3">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="O36" s="3">
         <v>0</v>
       </c>
       <c r="P36" s="3">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="Q36" s="3">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="R36" s="3">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="S36" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19434,16 +19364,16 @@
         <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>458</v>
+        <v>42</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>460</v>
+        <v>474</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>454</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>46</v>
@@ -19458,31 +19388,31 @@
         <v>2</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="M37" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N37" s="3">
-        <v>579</v>
+        <v>531</v>
       </c>
       <c r="O37" s="3">
         <v>0</v>
       </c>
       <c r="P37" s="3">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="Q37" s="3">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="R37" s="3">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S37" s="3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19493,16 +19423,16 @@
         <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>458</v>
+        <v>50</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>479</v>
+        <v>71</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>460</v>
+        <v>52</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>480</v>
+        <v>72</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>46</v>
@@ -19517,31 +19447,31 @@
         <v>2</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>462</v>
+        <v>54</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>481</v>
+        <v>73</v>
       </c>
       <c r="M38" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="N38" s="3">
-        <v>531</v>
+        <v>483</v>
       </c>
       <c r="O38" s="3">
         <v>0</v>
       </c>
       <c r="P38" s="3">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Q38" s="3">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="R38" s="3">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="S38" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19552,16 +19482,16 @@
         <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>71</v>
+        <v>477</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>72</v>
+        <v>478</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>46</v>
@@ -19576,31 +19506,31 @@
         <v>2</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>73</v>
+        <v>479</v>
       </c>
       <c r="M39" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N39" s="3">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="O39" s="3">
         <v>0</v>
       </c>
       <c r="P39" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q39" s="3">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="R39" s="3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="S39" s="3">
-        <v>100</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19614,13 +19544,13 @@
         <v>42</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>44</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>46</v>
@@ -19638,28 +19568,28 @@
         <v>48</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="M40" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N40" s="3">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="O40" s="3">
         <v>0</v>
       </c>
       <c r="P40" s="3">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="Q40" s="3">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="R40" s="3">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="S40" s="3">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19670,16 +19600,16 @@
         <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>485</v>
+        <v>74</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>486</v>
+        <v>75</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>46</v>
@@ -19694,31 +19624,31 @@
         <v>2</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>487</v>
+        <v>76</v>
       </c>
       <c r="M41" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" s="3">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="O41" s="3">
         <v>0</v>
       </c>
       <c r="P41" s="3">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="Q41" s="3">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="R41" s="3">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="S41" s="3">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19729,16 +19659,16 @@
         <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>46</v>
@@ -19753,31 +19683,31 @@
         <v>2</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M42" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N42" s="3">
-        <v>410</v>
+        <v>231</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
       <c r="P42" s="3">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Q42" s="3">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="R42" s="3">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="S42" s="3">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19788,16 +19718,16 @@
         <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>46</v>
@@ -19812,31 +19742,31 @@
         <v>2</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M43" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" s="3">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="O43" s="3">
         <v>0</v>
       </c>
       <c r="P43" s="3">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q43" s="3">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="R43" s="3">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="S43" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19850,13 +19780,13 @@
         <v>50</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>46</v>
@@ -19874,25 +19804,25 @@
         <v>54</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M44" s="3">
         <v>1</v>
       </c>
       <c r="N44" s="3">
-        <v>192</v>
+        <v>23</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="Q44" s="3">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="R44" s="3">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -19906,16 +19836,16 @@
         <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>52</v>
+        <v>300</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>46</v>
@@ -19927,34 +19857,34 @@
         <v>40</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>54</v>
+        <v>333</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>85</v>
+        <v>304</v>
       </c>
       <c r="M45" s="3">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="N45" s="3">
-        <v>23</v>
+        <v>26421</v>
       </c>
       <c r="O45" s="3">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P45" s="3">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="Q45" s="3">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="R45" s="3">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19968,13 +19898,13 @@
         <v>42</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>300</v>
+        <v>334</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>46</v>
@@ -19992,28 +19922,28 @@
         <v>333</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="M46" s="3">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="N46" s="3">
-        <v>26421</v>
+        <v>7096</v>
       </c>
       <c r="O46" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="P46" s="3">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="Q46" s="3">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R46" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S46" s="3">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20027,13 +19957,13 @@
         <v>42</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>46</v>
@@ -20051,28 +19981,28 @@
         <v>333</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="M47" s="3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N47" s="3">
-        <v>7096</v>
+        <v>6121</v>
       </c>
       <c r="O47" s="3">
         <v>3</v>
       </c>
       <c r="P47" s="3">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q47" s="3">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="R47" s="3">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="S47" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20086,13 +20016,13 @@
         <v>42</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>46</v>
@@ -20110,28 +20040,28 @@
         <v>333</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>340</v>
+        <v>315</v>
       </c>
       <c r="M48" s="3">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="N48" s="3">
-        <v>6121</v>
+        <v>5443</v>
       </c>
       <c r="O48" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P48" s="3">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="Q48" s="3">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="R48" s="3">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="S48" s="3">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20145,13 +20075,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>311</v>
+        <v>483</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>335</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>46</v>
@@ -20169,28 +20099,28 @@
         <v>333</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>315</v>
+        <v>485</v>
       </c>
       <c r="M49" s="3">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="N49" s="3">
-        <v>5443</v>
+        <v>5233</v>
       </c>
       <c r="O49" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P49" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q49" s="3">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="R49" s="3">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="S49" s="3">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20201,19 +20131,19 @@
         <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>450</v>
+        <v>87</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>335</v>
+        <v>88</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>488</v>
+        <v>89</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>47</v>
@@ -20225,31 +20155,31 @@
         <v>3</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>333</v>
+        <v>90</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>454</v>
+        <v>91</v>
       </c>
       <c r="M50" s="3">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="N50" s="3">
-        <v>5233</v>
+        <v>4522</v>
       </c>
       <c r="O50" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P50" s="3">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="Q50" s="3">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="R50" s="3">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="S50" s="3">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20260,19 +20190,19 @@
         <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>87</v>
+        <v>486</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>88</v>
+        <v>335</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>89</v>
+        <v>487</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>47</v>
@@ -20284,31 +20214,31 @@
         <v>3</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>90</v>
+        <v>333</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>91</v>
+        <v>488</v>
       </c>
       <c r="M51" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N51" s="3">
-        <v>4522</v>
+        <v>2198</v>
       </c>
       <c r="O51" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P51" s="3">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="Q51" s="3">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="R51" s="3">
         <v>3.1</v>
       </c>
       <c r="S51" s="3">
-        <v>8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20322,13 +20252,13 @@
         <v>42</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>489</v>
+        <v>342</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>335</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>490</v>
+        <v>343</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>46</v>
@@ -20346,28 +20276,28 @@
         <v>333</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>491</v>
+        <v>344</v>
       </c>
       <c r="M52" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="N52" s="3">
-        <v>2198</v>
+        <v>2041</v>
       </c>
       <c r="O52" s="3">
         <v>2</v>
       </c>
       <c r="P52" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q52" s="3">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="R52" s="3">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="S52" s="3">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20381,13 +20311,13 @@
         <v>42</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>342</v>
+        <v>489</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>335</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>343</v>
+        <v>490</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>46</v>
@@ -20405,28 +20335,28 @@
         <v>333</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>344</v>
+        <v>491</v>
       </c>
       <c r="M53" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N53" s="3">
-        <v>2041</v>
+        <v>1852</v>
       </c>
       <c r="O53" s="3">
         <v>2</v>
       </c>
       <c r="P53" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="Q53" s="3">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="R53" s="3">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S53" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20440,13 +20370,13 @@
         <v>42</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>335</v>
+        <v>92</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>493</v>
+        <v>94</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>46</v>
@@ -20461,31 +20391,31 @@
         <v>3</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>333</v>
+        <v>95</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="M54" s="3">
-        <v>16</v>
-      </c>
-      <c r="N54" s="3">
-        <v>1852</v>
-      </c>
-      <c r="O54" s="3">
-        <v>2</v>
-      </c>
-      <c r="P54" s="3">
-        <v>80</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>60</v>
-      </c>
-      <c r="R54" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="S54" s="3">
-        <v>20</v>
+        <v>40</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20499,13 +20429,13 @@
         <v>42</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>93</v>
+        <v>345</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>346</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>94</v>
+        <v>347</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>46</v>
@@ -20520,7 +20450,7 @@
         <v>3</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>40</v>
@@ -20544,65 +20474,6 @@
         <v>40</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J56" s="3">
-        <v>3</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="S56" s="3" t="s">
         <v>40</v>
       </c>
     </row>

--- a/yandex-direct/audit/2026-09-28-dnevnik-plan-vse-gruppy.xlsx
+++ b/yandex-direct/audit/2026-09-28-dnevnik-plan-vse-gruppy.xlsx
@@ -1102,11 +1102,11 @@
 Группа № 5774336316 - Перегородки-гармошки | Заказ</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] [заказ]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] [заказ]», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t xml:space="preserve">5 867₽ / 45 кл / 1 лид / CPL 5 867 / отказ 25% / об.трафика 89 / премиум 49% / поз. 2,4
-Структура «группа = фраза»: спрос «гармошка» переезжает в НЧ вместе со своей группой, а не дописывается в чужую. В НЧ гармошка конвертит лучше: запросы с «гармошка» - 129 визитов / 5 лидов в НЧ против 142 / 2 в СЧ. Разница, вероятно, в посадочной: СЧ ведёт на /peregorodki-garmoshka/ (123 визита, 2 лида), НЧ «Складные | Гармошка» - на /skladnye-peregorodki-na-zakaz/ (109 визитов, 3 лида) [ГИПОТЕЗА, выборка мала]. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии уже стоит -складные.</t>
+Выдача Яндекса (Keys.so, топ-10): «складная перегородка» и «перегородка гармошка» - один продукт, соседние интенты: 2 общих URL и 4 общих домена, мост между ними - «стеклянная перегородка гармошка» (4-5 общих URL с обоими). Значит, это две группы, но в одной РК: сейчас один продукт куплен в двух РК с разными бюджетами. НЧ - дом механизмов, туда и переносим отдельным блоком. Посадочные: СЧ /peregorodki-garmoshka/ 123 визита / 2 лида, НЧ /skladnye.../ 109 / 3 - разница в пределах случайности, поэтому страницу не меняем, сравним 04.11. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии стоит -складные.</t>
   </si>
   <si>
     <t>14.10: копия получает показы и клики, CPC ≤ 150 ₽; 04.11: лиды «гармошка» в НЧ ≥ суммы НЧ+СЧ до переноса</t>
@@ -1133,11 +1133,11 @@
 Группа № 5774336314 - Перегородки-гармошки</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородки] [гармошка] -заказ -зонирования -купить -межкомнатная -складные -стеклянные», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t xml:space="preserve">3 936₽ / 37 кл / 1 лид / CPL 3 936 / отказ 29% / об.трафика 87 / премиум 68% / поз. 2,7
-Структура «группа = фраза»: спрос «гармошка» переезжает в НЧ вместе со своей группой, а не дописывается в чужую. В НЧ гармошка конвертит лучше: запросы с «гармошка» - 129 визитов / 5 лидов в НЧ против 142 / 2 в СЧ. Разница, вероятно, в посадочной: СЧ ведёт на /peregorodki-garmoshka/ (123 визита, 2 лида), НЧ «Складные | Гармошка» - на /skladnye-peregorodki-na-zakaz/ (109 визитов, 3 лида) [ГИПОТЕЗА, выборка мала]. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии уже стоит -складные.</t>
+Выдача Яндекса (Keys.so, топ-10): «складная перегородка» и «перегородка гармошка» - один продукт, соседние интенты: 2 общих URL и 4 общих домена, мост между ними - «стеклянная перегородка гармошка» (4-5 общих URL с обоими). Значит, это две группы, но в одной РК: сейчас один продукт куплен в двух РК с разными бюджетами. НЧ - дом механизмов, туда и переносим отдельным блоком. Посадочные: СЧ /peregorodki-garmoshka/ 123 визита / 2 лида, НЧ /skladnye.../ 109 / 3 - разница в пределах случайности, поэтому страницу не меняем, сравним 04.11. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии стоит -складные.</t>
   </si>
   <si>
     <t>5774336314</t>
@@ -1151,11 +1151,11 @@
 Группа № 5774336318 - Перегородки-гармошки | Межкомнатная</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [межкомнатная]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [межкомнатная]», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t xml:space="preserve">3 892₽ / 43 кл / 1 лид / CPL 3 892 / отказ 28% / об.трафика 88 / премиум 44% / поз. 2,2
-Структура «группа = фраза»: спрос «гармошка» переезжает в НЧ вместе со своей группой, а не дописывается в чужую. В НЧ гармошка конвертит лучше: запросы с «гармошка» - 129 визитов / 5 лидов в НЧ против 142 / 2 в СЧ. Разница, вероятно, в посадочной: СЧ ведёт на /peregorodki-garmoshka/ (123 визита, 2 лида), НЧ «Складные | Гармошка» - на /skladnye-peregorodki-na-zakaz/ (109 визитов, 3 лида) [ГИПОТЕЗА, выборка мала]. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии уже стоит -складные.</t>
+Выдача Яндекса (Keys.so, топ-10): «складная перегородка» и «перегородка гармошка» - один продукт, соседние интенты: 2 общих URL и 4 общих домена, мост между ними - «стеклянная перегородка гармошка» (4-5 общих URL с обоими). Значит, это две группы, но в одной РК: сейчас один продукт куплен в двух РК с разными бюджетами. НЧ - дом механизмов, туда и переносим отдельным блоком. Посадочные: СЧ /peregorodki-garmoshka/ 123 визита / 2 лида, НЧ /skladnye.../ 109 / 3 - разница в пределах случайности, поэтому страницу не меняем, сравним 04.11. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии стоит -складные.</t>
   </si>
   <si>
     <t>5774336318</t>
@@ -1191,11 +1191,11 @@
 Группа № 5774336315 - Перегородки-гармошки | Купить</t>
   </si>
   <si>
-    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [купить]», минус-слова группы, объявления). В копии заменить ссылку объявлений: /peregorodki-garmoshka/ → /mezhkomnatnye-peregorodki-na-zakaz/skladnye-peregorodki-na-zakaz/ (UTM-шаблон оставить). Оригинал в СЧ - пауза (шаг 2).</t>
+    <t>Скопировать группу в РК НЧ 712877525 целиком (фраза «[перегородка] [гармошка] [купить]», минус-слова группы, объявления). Ссылку объявлений оставить /peregorodki-garmoshka/ (страница под слово «гармошка»). В НЧ это отдельный блок «Гармошка», в «Складные» не сливать. Оригинал в СЧ - пауза (шаг 2).</t>
   </si>
   <si>
     <t xml:space="preserve">1 406₽ / 21 кл / 0 лид / отказ 40% / об.трафика 89 / премиум 55% / поз. 2,2
-Структура «группа = фраза»: спрос «гармошка» переезжает в НЧ вместе со своей группой, а не дописывается в чужую. В НЧ гармошка конвертит лучше: запросы с «гармошка» - 129 визитов / 5 лидов в НЧ против 142 / 2 в СЧ. Разница, вероятно, в посадочной: СЧ ведёт на /peregorodki-garmoshka/ (123 визита, 2 лида), НЧ «Складные | Гармошка» - на /skladnye-peregorodki-na-zakaz/ (109 визитов, 3 лида) [ГИПОТЕЗА, выборка мала]. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии уже стоит -складные.</t>
+Выдача Яндекса (Keys.so, топ-10): «складная перегородка» и «перегородка гармошка» - один продукт, соседние интенты: 2 общих URL и 4 общих домена, мост между ними - «стеклянная перегородка гармошка» (4-5 общих URL с обоими). Значит, это две группы, но в одной РК: сейчас один продукт куплен в двух РК с разными бюджетами. НЧ - дом механизмов, туда и переносим отдельным блоком. Посадочные: СЧ /peregorodki-garmoshka/ 123 визита / 2 лида, НЧ /skladnye.../ 109 / 3 - разница в пределах случайности, поэтому страницу не меняем, сравним 04.11. Конфликта с НЧ 5774336420 [складные] [перегородки] [гармошка] нет: во фразе копии стоит -складные.</t>
   </si>
   <si>
     <t>5774336315</t>
